--- a/resources/ai-for-your-business/files/aifyb-int-rollout-plan.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-int-rollout-plan.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,11 +65,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -159,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,8 +190,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -604,7 +597,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>sort-it, answer-it work AI is genuinely good at (hands/judgement=1, language/data over and over=5).</t>
+          <t>sort-it, answer-it work AI is genuinely good at (hands/judgment=1, language/data over and over=5).</t>
         </is>
       </c>
     </row>
@@ -615,7 +608,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -723,8 +715,6 @@
       </c>
       <c r="E16" s="5" t="n"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
@@ -739,7 +729,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
@@ -806,7 +795,6 @@
       <c r="D27" s="10" t="n"/>
       <c r="E27" s="11" t="n"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
@@ -865,7 +853,6 @@
       </c>
       <c r="B35" s="6" t="inlineStr"/>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
@@ -880,7 +867,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
@@ -894,10 +880,6 @@
           <t>ePORTS — your ecom source. eports.global</t>
         </is>
       </c>
-    </row>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/resources/ai-for-your-business/files/aifyb-int-rollout-plan.xlsx
+++ b/resources/ai-for-your-business/files/aifyb-int-rollout-plan.xlsx
@@ -877,7 +877,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
